--- a/task263/golden/pfas_design_grants_2027.xlsx
+++ b/task263/golden/pfas_design_grants_2027.xlsx
@@ -258,7 +258,7 @@
     <t>Water pumped by the listed systems' wells, 2025 (million gallons)</t>
   </si>
   <si>
-    <t>People who get their water from those wells</t>
+    <t>People living in the county who get their water from any of those wells</t>
   </si>
   <si>
     <t>Total</t>
@@ -282,7 +282,7 @@
     <t>Counties. Water: the 2025 monthly operating reports for the listed systems' wells, each meter counted once a month (Lindvik Lake, Halvorsen, Skogen and Elvholm Falls each have two wells on one header meter, written on both wells' lines); Ackerholt Creek's September purchase through its emergency interconnect is not well water and is left out; Kesselring's emergency well (three days in July) is in.</t>
   </si>
   <si>
-    <t>People: each listed system's own customers plus the customers of every system that buys all its water from it, directly or through another buyer, on the connections in service (Solberg Lake's emergency tie and Hagestad Corners' purchase, closed 30 June 2025, are left out), counted in the county where the buyer is.</t>
+    <t>People: each listed system's own customers plus the customers of every system that buys all its water from it, directly or through another buyer, on the connections in service (Solberg Lake's emergency tie and Hagestad Corners' purchase, closed 30 June 2025, are left out), counted in the county where the buyer is. Four buyers are on the connections under an id the register holds as inactive beside an active system of the same name and county; each is counted as that active system, at its current population.</t>
   </si>
 </sst>
 </file>
@@ -2795,7 +2795,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
